--- a/var/data/original_files/Articles A September 7.xlsx
+++ b/var/data/original_files/Articles A September 7.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,11 +488,6 @@
           <t>Full Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinates</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure, Environment</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,36 +539,35 @@
           <t>https://www.msn.com/en-ae/news/middleeast/houthis-launch-missile-at-israeli-owned-tanker-near-saudi-port-of-yanbu/ar-AA1LCrnR?cvid=87122f717a8e4103c42cad2bf43c296b&amp;ocid=feed-health-article</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houthis launch missile at Israeli-owned tanker near Saudi port of Yanbu</t>
+          <t>Building America’s Biosurveillance Radar: AI and Metagenomics for Early Pathogen Detection</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yanbu</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45901</v>
+        <v>45904</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -583,7 +577,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -593,10 +587,9 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-ae/news/middleeast/houthis-launch-missile-at-israeli-owned-tanker-near-saudi-port-of-yanbu/ar-AA1LCrnR?cvid=87122f717a8e4103c42cad2bf43c296b&amp;ocid=feed-health-article</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>https://globalbiodefense.com/2025/09/04/scaling-pathogen-detection-ai-metagenomics-us-biosurveillance/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -611,17 +604,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Building America’s Biosurveillance Radar: AI and Metagenomics for Early Pathogen Detection</t>
+          <t>New Sensor Design Offers Ultra-Sensitive Detection Using Nanomaterials</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -645,35 +638,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/09/04/scaling-pathogen-detection-ai-metagenomics-us-biosurveillance/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>https://globalbiodefense.com/2025/09/04/breakthrough-biosensor-nanomaterials-dna-detection/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New Sensor Design Offers Ultra-Sensitive Detection Using Nanomaterials</t>
+          <t>Update 312 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Zaporizhzhya</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -687,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,67 +689,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/09/04/breakthrough-biosensor-nanomaterials-dna-detection/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-312-iaea-director-general-statement-on-situation-in-ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Update 312 – IAEA Director General Statement on Situation in Ukraine</t>
+          <t>Democratic Republic of the Congo declares Ebola virus disease outbreak in Kasai Province</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Democratic Republic of Congo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zaporizhzhya</t>
+          <t>Kasai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-312-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>https://www.afro.who.int/countries/democratic-republic-of-congo/news/democratic-republic-congo-declares-ebola-virus-disease-outbreak-kasai-province</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -767,27 +757,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo declares Ebola virus disease outbreak in Kasai Province</t>
+          <t>Mpox Resurgence: A Global Wake-Up Call for Zoonotic Disease Preparedness</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Democratic Republic of Congo</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kasai</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -801,10 +791,9 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.afro.who.int/countries/democratic-republic-of-congo/news/democratic-republic-congo-declares-ebola-virus-disease-outbreak-kasai-province</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>https://globalbiodefense.com/2025/09/04/mpox-global-resurgence-health-security/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -814,26 +803,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mpox Resurgence: A Global Wake-Up Call for Zoonotic Disease Preparedness</t>
+          <t>Russia is ready to discuss nuclear fuel at Ukraine’s Zaporizhzhia with US</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Zaporizhzhya</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -843,20 +832,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/09/04/mpox-global-resurgence-health-security/</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>https://english.alarabiya.net/News/world/2025/09/05/russia-is-ready-to-discuss-nuclear-fuel-at-ukraine-s-zaporizhzhia-with-us</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -871,21 +859,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia is ready to discuss nuclear fuel at Ukraine’s Zaporizhzhia with US</t>
+          <t>Iran and IAEA to resume nuclear inspection talks in Vienna with uranium stockpile in question</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zaporizhzhya</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45905</v>
+        <v>45904</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -905,15 +893,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/world/2025/09/05/russia-is-ready-to-discuss-nuclear-fuel-at-ukraine-s-zaporizhzhia-with-us</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>https://www.thenationalnews.com/news/mena/2025/09/04/iran-and-iaea-to-resume-nuclear-inspection-talks-in-vienna-with-uranium-stockpile-in-question/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -923,17 +910,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran and IAEA to resume nuclear inspection talks in Vienna with uranium stockpile in question</t>
+          <t>Jellyfish disrupt French nuclear power plant for second time in a month</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Paluel</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -957,15 +944,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/news/mena/2025/09/04/iran-and-iaea-to-resume-nuclear-inspection-talks-in-vienna-with-uranium-stockpile-in-question/</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>https://www.bbc.com/news/articles/c5ygkxlmg41o</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -975,17 +961,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jellyfish disrupt French nuclear power plant for second time in a month</t>
+          <t>Nuclear Weapons At China’s 2025 Victory Day Parade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paluel</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -999,7 +985,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1009,10 +995,9 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c5ygkxlmg41o</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>https://fas.org/publication/nuclear-weapons-at-chinas-2025-victory-day-parade/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1027,17 +1012,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nuclear Weapons At China’s 2025 Victory Day Parade</t>
+          <t>Iran’s security chief, UK counterpart discuss nuclear talks, snapback</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1051,7 +1036,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1061,10 +1046,9 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://fas.org/publication/nuclear-weapons-at-chinas-2025-victory-day-parade/</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>https://www.iranintl.com/en/202509042837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1079,17 +1063,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran’s security chief, UK counterpart discuss nuclear talks, snapback</t>
+          <t>US military base to host study of meltdown-proof nuclear microreactor technology</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1113,15 +1097,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202509042837</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>https://interestingengineering.com/energy/us-air-force-base-nuclear-microreactor</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1131,17 +1114,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US military base to host study of meltdown-proof nuclear microreactor technology</t>
+          <t>Iran Prioritizes Removal and Dispersal of Industrial Chillers at Natanz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Natanz</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1165,10 +1148,9 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/energy/us-air-force-base-nuclear-microreactor</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>https://isis-online.org/isis-reports/iran-prioritizes-removal-and-dispersal-of-industrial-chillers-at-natanz-what-does-it-mean-for-the-enrichment-site</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1183,7 +1165,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Prioritizes Removal and Dispersal of Industrial Chillers at Natanz</t>
+          <t>Iran increased stockpile of near weapons-grade uranium before Israeli attack, UN agency says</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1193,11 +1175,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Natanz</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45904</v>
+        <v>45903</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1207,7 +1189,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1217,10 +1199,9 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://isis-online.org/isis-reports/iran-prioritizes-removal-and-dispersal-of-industrial-chillers-at-natanz-what-does-it-mean-for-the-enrichment-site</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>https://apnews.com/article/iran-nuclear-iaea-weapons-grade-uranium-c3ae6a8aae96d54355df73842916a324</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1235,7 +1216,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran increased stockpile of near weapons-grade uranium before Israeli attack, UN agency says</t>
+          <t>Iran Update, September 2, 2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1249,7 +1230,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45903</v>
+        <v>45902</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1259,7 +1240,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1269,39 +1250,38 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/iran-nuclear-iaea-weapons-grade-uranium-c3ae6a8aae96d54355df73842916a324</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>https://understandingwar.org/research/middle-east/iran-update-september-2-2025/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Biological, Radiological, Nuclear</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Update, September 2, 2025</t>
+          <t>EU launches new health funding calls to boost crisis preparedness</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Saint-Josse-ten-Noode</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1321,10 +1301,9 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://understandingwar.org/research/middle-east/iran-update-september-2-2025/</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>https://www.openaccessgovernment.org/eu-launches-new-health-funding-calls-to-boost-crisis-preparedness/197762/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1339,17 +1318,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EU launches new health funding calls to boost crisis preparedness</t>
+          <t>Yemeni minister accuses Houthi rebels of manufacturing chemical weapons</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saint-Josse-ten-Noode</t>
+          <t>Sanaa</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1363,49 +1342,48 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.openaccessgovernment.org/eu-launches-new-health-funding-calls-to-boost-crisis-preparedness/197762/</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>https://www.thenationalnews.com/news/mena/2025/09/04/yemeni-minister-accuses-houthi-rebels-of-manufacturing-chemical-weapons/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EU launches new health funding calls to boost crisis preparedness</t>
+          <t>OPCW analytical chemistry course underway at Protechnik</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saint-Josse-ten-Noode</t>
+          <t>Gauteng</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45904</v>
+        <v>45902</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1415,7 +1393,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1425,218 +1403,9 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.openaccessgovernment.org/eu-launches-new-health-funding-calls-to-boost-crisis-preparedness/197762/</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>EU launches new health funding calls to boost crisis preparedness</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Saint-Josse-ten-Noode</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>https://www.openaccessgovernment.org/eu-launches-new-health-funding-calls-to-boost-crisis-preparedness/197762/</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>EU launches new health funding calls to boost crisis preparedness</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Saint-Josse-ten-Noode</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>https://www.openaccessgovernment.org/eu-launches-new-health-funding-calls-to-boost-crisis-preparedness/197762/</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yemeni minister accuses Houthi rebels of manufacturing chemical weapons</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Sanaa</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>https://www.thenationalnews.com/news/mena/2025/09/04/yemeni-minister-accuses-houthi-rebels-of-manufacturing-chemical-weapons/</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OPCW analytical chemistry course underway at Protechnik</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Gauteng</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>45902</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
           <t>https://www.defenceweb.co.za/industry/industry-industry/opcw-analytical-chemistry-course-underway-at-protechnik/</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
